--- a/www/sosdar-StatsInExcel-MatchScoreWizzard-SpanishSampleForm.xlsx
+++ b/www/sosdar-StatsInExcel-MatchScoreWizzard-SpanishSampleForm.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5266823fe773b5e1/downloads/MatchScoreWizzard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sos\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{84A8701A-A826-4691-B85E-8574889CBE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55C5DCBE-246F-46FD-87AF-D7ACAC9745F3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E75DDC0-117F-4672-B4BA-1867649BC831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{EBB2CA61-FEA4-4302-A819-98635C214671}"/>
   </bookViews>
   <sheets>
-    <sheet name="FORM" sheetId="3" r:id="rId1"/>
+    <sheet name="FORM" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="53">
   <si>
     <t>E-Mail</t>
   </si>
@@ -104,6 +104,19 @@
     <t>Algeria</t>
   </si>
   <si>
+    <t>Name or
+Nickname</t>
+  </si>
+  <si>
+    <t>MATCH</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>YOUR PREDICTIONS</t>
+  </si>
+  <si>
     <t>South Africa</t>
   </si>
   <si>
@@ -173,43 +186,585 @@
     <t>Uzbekistan</t>
   </si>
   <si>
-    <t>MatchScore Wizzard - Copa Mundo 2026 Fase de Grupos</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Presiona la tecla </t>
+    <r>
+      <t xml:space="preserve">Use the </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
+        <color indexed="60"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tab</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color indexed="60"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> key to navigate between cells</t>
+    </r>
+  </si>
+  <si>
+    <t>MatchScore Wizzard - Copa Mundo 2026 Groups Stage</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+Bienvenido al concurso “MatchScore Wizzard – </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fase de Grupos Copa Mundo 2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">”, que se llevará a cabo durante los </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>72</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> partidos de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>la fase de grupos de la Copa Mundial 2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Los detalles del concurso se describen a continuación.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1. Inscripción</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+La inscripción es completamente gratuita y se gestionará de forma electrónica (NO es necesario imprimir el formulario). Complete su formulario utilizando Microsoft Excel. Ingrese: nombre completo o apodo (por ejemplo, “</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lio Messi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>” o “</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Best of the World</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">”), correo electrónico y sus pronósticos para cada partido. Luego, presione </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>F12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> para guardar su formulario con un nombre como, por ejemplo, “</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lionel Messi.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>” o “</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Best of the World.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">”. Envíe su formulario a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AdminEmail@domain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> antes del inicio de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>la Copa Mundo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, el </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>11 de Junio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2. Sistema de puntuación</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Por cada partido usted podrá obtener entre cero (0) y tres (3) puntos, de acuerdo con las siguientes reglas:
+■ Tres (3) puntos si su pronóstico coincide exactamente con el marcador final oficial._x000B_■ Dos (2) puntos si acierta el equipo ganador y los goles anotados por uno de los dos equipos, pero no por ambos._x000B_■ Un (1) punto si acierta que el partido termina empatado, pero no acierta el número exacto de goles anotados._x000B_■ Cero (0) puntos si no acierta el equipo ganador ni el empate.
+Ejemplo:_x000B_El resultado oficial del partido A vs B es </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2-0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> a favor de A._x000B_Si su pronóstico fue </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> a favor del equipo A, obtendrá tres puntos._x000B_Si su pronóstico fue </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1, 1-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 3-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 4-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 5-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, … a favor del equipo A, obtendrá dos puntos, ya que acertó al ganador y los goles de uno de los dos equipos._x000B_Si su pronóstico fue 3-1, 4-1, 5-1…, 3-2, 4-2, 5-2… o cualquier otro marcador a favor del equipo A, obtendrá un punto, ya que acertó el equipo ganador, pero no acertó los goles anotados por ninguno de los dos equipos._x000B_Si su pronóstico fue victoria del equipo B o un empate, obtendrá cero puntos.
+Su puntaje final será la suma total de puntos obtenidos en los </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>72</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> partidos.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3. Licencia y uso</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Este formulario de Excel se proporciona únicamente para uso personal y no comercial, como parte de una actividad de entretenimiento. Usted puede utilizarlo y adaptarlo para concursos amistosos de pronósticos. No se permite su uso comercial, reventa ni redistribución como producto propio.
+_x000B_</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4. Derechos de autor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+© MatchScore Wizzard. Todos los derechos reservados._x000B_El diseño, la estructura, el texto y la presentación de este archivo están protegidos por las leyes de derechos de autor.
+_x000B_</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5. Aviso de entretenimiento únicamente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Este concurso y su sistema de puntuación están destinados exclusivamente a fines de entretenimiento._x000B_No hay apuestas, juegos de azar, premios ni recompensas económicas involucradas.
+_x000B_</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6. Concursos independientes y afiliaciones</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Cada concurso que utilice este formulario es organizado de manera independiente por su administrador._x000B_MatchScore Wizzard no gestiona concursos ni está afiliado a organizadores, participantes ni a ninguna autoridad deportiva.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
         <color rgb="FFC00000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Tab</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> para avanzar</t>
-    </r>
-  </si>
-  <si>
-    <t>Nombre o apodo</t>
-  </si>
-  <si>
-    <t>Juego</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Tus predicciones</t>
+      <t>❤️</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Apoyo opcional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Si disfrutas utilizar MatchScore Wizzard y desea apoyar su desarrollo continuo, se agradecen contribuciones voluntarias y no deducibles de impuestos._x000B_El apoyo es opcional y no afecta la participación, la puntuación ni los resultados._x000B_(Puede ir a https://paypal.me/blessingSOSDAR, usar la cuenta PayPal polluelo02@hotmail.com, o hacer click o escanear el código QR que se muestra a continuación).
+</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -219,14 +774,21 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color indexed="60"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="8"/>
+      <sz val="9"/>
+      <color indexed="60"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -270,8 +832,29 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
+      <sz val="8"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="8"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -354,19 +937,13 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -374,66 +951,78 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -444,9 +1033,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF1F78B4"/>
       <color rgb="FFA6CEE3"/>
       <color rgb="FFFC8D62"/>
-      <color rgb="FF1F78B4"/>
       <color rgb="FFFF7F00"/>
       <color rgb="FFE5C494"/>
       <color rgb="FFFDBF6F"/>
@@ -465,920 +1054,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>22654</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>781</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>819288</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>36634</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1027" name="Text Box 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8A14F2B-36C3-04BA-5266-7E6BB5576CED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="22654" y="372012"/>
-          <a:ext cx="3119269" cy="11802891"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="0">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Bienvenido al “</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>MatchScore Wizzard – Concurso de la Fase de Grupos de la Copa Mundial 2026</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="0">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>”, que se llevará a cabo durante los</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> 72 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="0">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>partidos de</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> la fase de grupos de la Copa Mundial 2026. </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Los detalles del concurso se</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" baseline="0">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> describen a continuación.</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>1. Inscripción</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>La inscripción es completamente gratuita y se gestionará de forma electrónica (NO es necesario imprimir el formulario). Complete su formulario utilizando Microsoft Excel. Ingrese: nombre completo o apodo (por ejemplo, “Lio Messi” o “Best of the World”), correo electrónico y sus pronósticos para cada partido. Luego, presione </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>F12</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> para guardar su formulario con un nombre como, por ejemplo, “</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Lionel Messi.xlsx</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>” o “</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Best of the World.xlsx</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>”. Envíe su formulario a </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>AdminEmail@domain</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> (un archivo xlsx por cada formulario) antes del inicio de </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>la Copa Mundo</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>, el </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>11 de junio</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>2. Sistema de puntuación</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Por cada partido usted podrá obtener entre cero (0) y tres (3) puntos, de acuerdo con las siguientes reglas:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>■ </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Tres (3) puntos</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> si su pronóstico coincide exactamente con el marcador final oficial.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>■ </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Dos (2) puntos</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> si acierta el equipo ganador y los goles anotados por uno de los dos equipos, pero no por ambos.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>■ </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Un (1) punto</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> si acierta que el partido termina empatado, pero no acierta el número exacto de goles anotados.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>■ </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Cero (0) puntos</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> si no acierta el equipo ganador ni el empate.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Ejemplo:</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>El resultado oficial del partido A vs B es </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>2-0</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> a favor de A.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Si su pronóstico fue </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1" u="sng">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1" u="none">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>-</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1" u="sng">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>0</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1" u="none">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>a favor del equipo A, obtendrá </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>tres puntos</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Si su pronóstico fue </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1" u="sng">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>-1, 1-</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1" u="sng">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>0</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>, 3-</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1" u="sng">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>0</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>, 4-</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1" u="sng">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>0</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>, 5-</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1" u="sng">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>0</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>, … a favor del equipo A, obtendrá </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>dos puntos</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>, ya que acertó al ganador y los goles de uno de los dos equipos.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Si su pronóstico fue 3-1, 4-1, 5-1…, 3-2, 4-2, 5-2… o cualquier otro marcador a favor del equipo A, obtendrá </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>un punto</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>, ya que acertó el equipo ganador, pero no acertó los goles anotados por ninguno de los dos equipos.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Si su pronóstico fue victoria del equipo B o un empate, obtendrá </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>cero puntos</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Su puntaje final será la suma total de puntos obtenidos en los </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>72 partidos</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>3. Licencia y uso</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Este formulario de Excel se proporciona únicamente para uso personal y no comercial, como parte de una actividad de entretenimiento. Usted puede utilizarlo y adaptarlo para concursos amistosos de pronósticos.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" baseline="0">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>No se permite su uso comercial, reventa ni redistribución como producto propio.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>4. Derechos de autor</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>© MatchScore Wizzard. Todos los derechos reservados.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>El diseño, la estructura, el texto y la presentación de este archivo están protegidos por las leyes de derechos de autor.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>5. Aviso de entretenimiento únicamente</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Este concurso y su sistema de puntuación están destinados </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>exclusivamente a fines de entretenimiento</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>No hay apuestas, juegos de azar, premios ni recompensas económicas involucradas.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>6. Concursos independientes y afiliaciones</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Cada concurso que utilice este formulario es organizado de manera independiente por su administrador.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>MatchScore Wizzard no gestiona concursos ni está afiliado a organizadores, participantes ni a ninguna autoridad deportiva.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>❤️ Apoyo opcional</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Si disfrutas utilizar MatchScore Wizzard y desea apoyar su desarrollo continuo, se agradecen contribuciones voluntarias y no deducibles de impuestos.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>El apoyo es opcional y no afecta la participación, la puntuación ni los resultados.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>(Puede utilizar la cuenta de PayPal </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800" b="1">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>polluelo02@hotmail.com</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="800">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> o el código QR que se muestra a continuación).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="800">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="en-US" sz="800" b="1">
-            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1394,10 +1069,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1026" name="Text Box 2">
+        <xdr:cNvPr id="3" name="Text Box 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E488B4-6263-E538-43BA-256F6BD00DC2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6B217DA-022C-4749-BC58-0CFD8C5B42B2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1407,8 +1082,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="9404350"/>
-          <a:ext cx="0" cy="8788400"/>
+          <a:off x="0" y="12204700"/>
+          <a:ext cx="0" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1873,22 +1548,23 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>341422</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>117664</xdr:rowOff>
+      <xdr:colOff>180497</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>148110</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>162651</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>29703</xdr:rowOff>
+      <xdr:colOff>1726</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>60149</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48B3DE83-8ED5-3952-3116-7A4B14647DCC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2B6CE36-3447-4F48-B646-A1813765B4E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1897,7 +1573,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1911,8 +1587,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="885086" y="9862304"/>
-          <a:ext cx="1602274" cy="1599574"/>
+          <a:off x="723422" y="9292110"/>
+          <a:ext cx="1602404" cy="1601139"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2305,7 +1981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29A7B56-6BD6-4BFE-9B6D-2424CEA35A53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4794D882-0076-4D28-9C89-2D7ECD9E5301}">
   <dimension ref="A1:L79"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="11.75" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -2324,44 +2000,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="A1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:12" ht="12" x14ac:dyDescent="0.6">
-      <c r="F2" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
+      <c r="A2" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
       <c r="F3" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="24"/>
+        <v>23</v>
+      </c>
+      <c r="G3" s="18"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="20"/>
     </row>
     <row r="4" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -2371,17 +2064,27 @@
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
       <c r="F5" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="20"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="23"/>
     </row>
     <row r="6" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
       <c r="F6" s="3"/>
       <c r="G6" s="4"/>
       <c r="H6" s="2"/>
@@ -2391,21 +2094,31 @@
       <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="5" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
+        <v>25</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
     </row>
     <row r="8" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="26"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
       <c r="F8" s="3">
         <v>1</v>
       </c>
@@ -2420,11 +2133,16 @@
         <v>1</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L8" s="7"/>
     </row>
     <row r="9" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="3">
         <v>2</v>
       </c>
@@ -2437,11 +2155,16 @@
         <v>1</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L9" s="7"/>
     </row>
     <row r="10" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
       <c r="F10" s="3">
         <v>3</v>
       </c>
@@ -2449,35 +2172,45 @@
         <v>46185</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L10" s="7"/>
     </row>
     <row r="11" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="3">
         <v>4</v>
       </c>
       <c r="G11" s="14"/>
       <c r="H11" s="11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
       <c r="F12" s="3">
         <v>5</v>
       </c>
@@ -2485,24 +2218,29 @@
         <v>46186</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L12" s="7"/>
     </row>
     <row r="13" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="3">
         <v>6</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="3" t="s">
@@ -2514,6 +2252,11 @@
       <c r="L13" s="7"/>
     </row>
     <row r="14" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
       <c r="F14" s="3">
         <v>7</v>
       </c>
@@ -2526,17 +2269,22 @@
         <v>1</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="3">
         <v>8</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="3" t="s">
@@ -2548,6 +2296,11 @@
       <c r="L15" s="7"/>
     </row>
     <row r="16" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
       <c r="F16" s="3">
         <v>9</v>
       </c>
@@ -2566,7 +2319,12 @@
       </c>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="3">
         <v>10</v>
       </c>
@@ -2579,11 +2337,16 @@
         <v>1</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L17" s="7"/>
     </row>
-    <row r="18" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
       <c r="F18" s="3">
         <v>11</v>
       </c>
@@ -2600,24 +2363,34 @@
       </c>
       <c r="L18" s="7"/>
     </row>
-    <row r="19" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="3">
         <v>12</v>
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L19" s="7"/>
     </row>
-    <row r="20" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="26"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="3">
         <v>13</v>
       </c>
@@ -2625,7 +2398,7 @@
         <v>46188</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="3" t="s">
@@ -2636,7 +2409,12 @@
       </c>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="3">
         <v>14</v>
       </c>
@@ -2649,28 +2427,38 @@
         <v>1</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L21" s="7"/>
     </row>
-    <row r="22" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
       <c r="F22" s="3">
         <v>15</v>
       </c>
       <c r="G22" s="14"/>
       <c r="H22" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L22" s="7"/>
     </row>
-    <row r="23" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
       <c r="F23" s="3">
         <v>16</v>
       </c>
@@ -2683,11 +2471,16 @@
         <v>1</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L23" s="7"/>
     </row>
-    <row r="24" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
       <c r="F24" s="3">
         <v>17</v>
       </c>
@@ -2702,28 +2495,38 @@
         <v>1</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L24" s="7"/>
     </row>
-    <row r="25" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
       <c r="F25" s="3">
         <v>18</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L25" s="7"/>
     </row>
-    <row r="26" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
       <c r="F26" s="3">
         <v>19</v>
       </c>
@@ -2736,28 +2539,38 @@
         <v>1</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L26" s="7"/>
     </row>
-    <row r="27" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="3">
         <v>20</v>
       </c>
       <c r="G27" s="14"/>
       <c r="H27" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L27" s="7"/>
     </row>
-    <row r="28" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
       <c r="F28" s="3">
         <v>21</v>
       </c>
@@ -2772,11 +2585,16 @@
         <v>1</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L28" s="7"/>
     </row>
-    <row r="29" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
       <c r="F29" s="3">
         <v>22</v>
       </c>
@@ -2793,13 +2611,18 @@
       </c>
       <c r="L29" s="7"/>
     </row>
-    <row r="30" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
       <c r="F30" s="3">
         <v>23</v>
       </c>
       <c r="G30" s="14"/>
       <c r="H30" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="3" t="s">
@@ -2810,13 +2633,18 @@
       </c>
       <c r="L30" s="7"/>
     </row>
-    <row r="31" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
       <c r="F31" s="3">
         <v>24</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I31" s="7"/>
       <c r="J31" s="3" t="s">
@@ -2827,7 +2655,12 @@
       </c>
       <c r="L31" s="7"/>
     </row>
-    <row r="32" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
       <c r="F32" s="3">
         <v>25</v>
       </c>
@@ -2835,24 +2668,29 @@
         <v>46191</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L32" s="7"/>
     </row>
-    <row r="33" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="26"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
       <c r="F33" s="3">
         <v>26</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I33" s="7"/>
       <c r="J33" s="3" t="s">
@@ -2863,24 +2701,34 @@
       </c>
       <c r="L33" s="7"/>
     </row>
-    <row r="34" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="26"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
       <c r="F34" s="3">
         <v>27</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L34" s="7"/>
     </row>
-    <row r="35" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="26"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
       <c r="F35" s="3">
         <v>28</v>
       </c>
@@ -2897,7 +2745,12 @@
       </c>
       <c r="L35" s="7"/>
     </row>
-    <row r="36" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
       <c r="F36" s="3">
         <v>29</v>
       </c>
@@ -2912,51 +2765,66 @@
         <v>1</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L36" s="7"/>
     </row>
-    <row r="37" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="26"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
       <c r="F37" s="3">
         <v>30</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L37" s="7"/>
     </row>
-    <row r="38" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="26"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
       <c r="F38" s="3">
         <v>31</v>
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L38" s="7"/>
     </row>
-    <row r="39" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="26"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
       <c r="F39" s="3">
         <v>32</v>
       </c>
       <c r="G39" s="14"/>
       <c r="H39" s="11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="3" t="s">
@@ -2967,7 +2835,12 @@
       </c>
       <c r="L39" s="7"/>
     </row>
-    <row r="40" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="26"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
       <c r="F40" s="3">
         <v>33</v>
       </c>
@@ -2986,7 +2859,12 @@
       </c>
       <c r="L40" s="7"/>
     </row>
-    <row r="41" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="26"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
       <c r="F41" s="3">
         <v>34</v>
       </c>
@@ -2999,17 +2877,22 @@
         <v>1</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L41" s="7"/>
     </row>
-    <row r="42" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="26"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
       <c r="F42" s="3">
         <v>35</v>
       </c>
       <c r="G42" s="14"/>
       <c r="H42" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="3" t="s">
@@ -3020,13 +2903,18 @@
       </c>
       <c r="L42" s="7"/>
     </row>
-    <row r="43" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="26"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
       <c r="F43" s="3">
         <v>36</v>
       </c>
       <c r="G43" s="14"/>
       <c r="H43" s="11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I43" s="7"/>
       <c r="J43" s="3" t="s">
@@ -3037,7 +2925,12 @@
       </c>
       <c r="L43" s="7"/>
     </row>
-    <row r="44" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="26"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
       <c r="F44" s="3">
         <v>37</v>
       </c>
@@ -3052,11 +2945,16 @@
         <v>1</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="26"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
       <c r="F45" s="3">
         <v>38</v>
       </c>
@@ -3069,11 +2967,16 @@
         <v>1</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L45" s="7"/>
     </row>
-    <row r="46" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="26"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
       <c r="F46" s="3">
         <v>39</v>
       </c>
@@ -3086,28 +2989,38 @@
         <v>1</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L46" s="7"/>
     </row>
-    <row r="47" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="26"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
       <c r="F47" s="3">
         <v>40</v>
       </c>
       <c r="G47" s="14"/>
       <c r="H47" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L47" s="7"/>
     </row>
-    <row r="48" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="26"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
       <c r="F48" s="3">
         <v>41</v>
       </c>
@@ -3115,24 +3028,29 @@
         <v>46195</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L48" s="7"/>
     </row>
-    <row r="49" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="26"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
       <c r="F49" s="3">
         <v>42</v>
       </c>
       <c r="G49" s="14"/>
       <c r="H49" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="3" t="s">
@@ -3143,7 +3061,12 @@
       </c>
       <c r="L49" s="7"/>
     </row>
-    <row r="50" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="26"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
       <c r="F50" s="3">
         <v>43</v>
       </c>
@@ -3156,17 +3079,22 @@
         <v>1</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="26"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
       <c r="F51" s="3">
         <v>44</v>
       </c>
       <c r="G51" s="14"/>
       <c r="H51" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I51" s="7"/>
       <c r="J51" s="3" t="s">
@@ -3177,7 +3105,12 @@
       </c>
       <c r="L51" s="7"/>
     </row>
-    <row r="52" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="26"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
       <c r="F52" s="3">
         <v>45</v>
       </c>
@@ -3196,13 +3129,18 @@
       </c>
       <c r="L52" s="7"/>
     </row>
-    <row r="53" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="26"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
       <c r="F53" s="3">
         <v>46</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I53" s="7"/>
       <c r="J53" s="3" t="s">
@@ -3213,7 +3151,12 @@
       </c>
       <c r="L53" s="7"/>
     </row>
-    <row r="54" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="26"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
       <c r="F54" s="3">
         <v>47</v>
       </c>
@@ -3226,17 +3169,22 @@
         <v>1</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L54" s="7"/>
     </row>
-    <row r="55" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="26"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
       <c r="F55" s="3">
         <v>48</v>
       </c>
       <c r="G55" s="15"/>
       <c r="H55" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="3" t="s">
@@ -3247,7 +3195,12 @@
       </c>
       <c r="L55" s="7"/>
     </row>
-    <row r="56" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="26"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
       <c r="F56" s="3">
         <v>49</v>
       </c>
@@ -3255,7 +3208,7 @@
         <v>46197</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="3" t="s">
@@ -3266,24 +3219,34 @@
       </c>
       <c r="L56" s="7"/>
     </row>
-    <row r="57" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="26"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
       <c r="F57" s="3">
         <v>50</v>
       </c>
       <c r="G57" s="14"/>
       <c r="H57" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L57" s="7"/>
     </row>
-    <row r="58" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="26"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
       <c r="F58" s="3">
         <v>51</v>
       </c>
@@ -3296,34 +3259,44 @@
         <v>1</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L58" s="7"/>
     </row>
-    <row r="59" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="26"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
       <c r="F59" s="3">
         <v>52</v>
       </c>
       <c r="G59" s="14"/>
       <c r="H59" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L59" s="7"/>
     </row>
-    <row r="60" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="26"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
       <c r="F60" s="3">
         <v>53</v>
       </c>
       <c r="G60" s="14"/>
       <c r="H60" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="3" t="s">
@@ -3334,13 +3307,18 @@
       </c>
       <c r="L60" s="7"/>
     </row>
-    <row r="61" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="26"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
       <c r="F61" s="3">
         <v>54</v>
       </c>
       <c r="G61" s="14"/>
       <c r="H61" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I61" s="7"/>
       <c r="J61" s="3" t="s">
@@ -3351,7 +3329,12 @@
       </c>
       <c r="L61" s="7"/>
     </row>
-    <row r="62" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="26"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
       <c r="F62" s="3">
         <v>55</v>
       </c>
@@ -3359,7 +3342,7 @@
         <v>46198</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I62" s="7"/>
       <c r="J62" s="3" t="s">
@@ -3370,7 +3353,12 @@
       </c>
       <c r="L62" s="7"/>
     </row>
-    <row r="63" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="26"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
       <c r="F63" s="3">
         <v>56</v>
       </c>
@@ -3387,13 +3375,18 @@
       </c>
       <c r="L63" s="7"/>
     </row>
-    <row r="64" spans="6:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="26"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
       <c r="F64" s="3">
         <v>57</v>
       </c>
       <c r="G64" s="14"/>
       <c r="H64" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="3" t="s">
@@ -3404,14 +3397,18 @@
       </c>
       <c r="L64" s="7"/>
     </row>
-    <row r="65" spans="4:12" ht="13" x14ac:dyDescent="0.6">
-      <c r="D65"/>
+    <row r="65" spans="1:12" ht="13" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="26"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
       <c r="F65" s="3">
         <v>58</v>
       </c>
       <c r="G65" s="14"/>
       <c r="H65" s="11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="3" t="s">
@@ -3422,30 +3419,40 @@
       </c>
       <c r="L65" s="7"/>
     </row>
-    <row r="66" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="26"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
       <c r="F66" s="3">
         <v>59</v>
       </c>
       <c r="G66" s="14"/>
       <c r="H66" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L66" s="7"/>
     </row>
-    <row r="67" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="26"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
       <c r="F67" s="3">
         <v>60</v>
       </c>
       <c r="G67" s="14"/>
       <c r="H67" s="11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="3" t="s">
@@ -3456,7 +3463,12 @@
       </c>
       <c r="L67" s="7"/>
     </row>
-    <row r="68" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="26"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
       <c r="F68" s="3">
         <v>61</v>
       </c>
@@ -3464,7 +3476,7 @@
         <v>46199</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I68" s="7"/>
       <c r="J68" s="3" t="s">
@@ -3475,47 +3487,62 @@
       </c>
       <c r="L68" s="7"/>
     </row>
-    <row r="69" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="26"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
       <c r="F69" s="3">
         <v>62</v>
       </c>
       <c r="G69" s="14"/>
       <c r="H69" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L69" s="7"/>
     </row>
-    <row r="70" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="26"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
       <c r="F70" s="3">
         <v>63</v>
       </c>
       <c r="G70" s="14"/>
       <c r="H70" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L70" s="7"/>
     </row>
-    <row r="71" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="26"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
       <c r="F71" s="3">
         <v>64</v>
       </c>
       <c r="G71" s="14"/>
       <c r="H71" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I71" s="7"/>
       <c r="J71" s="3" t="s">
@@ -3526,24 +3553,34 @@
       </c>
       <c r="L71" s="7"/>
     </row>
-    <row r="72" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="26"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
       <c r="F72" s="3">
         <v>65</v>
       </c>
       <c r="G72" s="14"/>
       <c r="H72" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K72" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L72" s="7"/>
     </row>
-    <row r="73" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="26"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
       <c r="F73" s="3">
         <v>66</v>
       </c>
@@ -3560,7 +3597,12 @@
       </c>
       <c r="L73" s="7"/>
     </row>
-    <row r="74" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="26"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
       <c r="F74" s="3">
         <v>67</v>
       </c>
@@ -3568,7 +3610,7 @@
         <v>46200</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="3" t="s">
@@ -3579,7 +3621,12 @@
       </c>
       <c r="L74" s="7"/>
     </row>
-    <row r="75" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="26"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
       <c r="F75" s="3">
         <v>68</v>
       </c>
@@ -3596,7 +3643,12 @@
       </c>
       <c r="L75" s="7"/>
     </row>
-    <row r="76" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="26"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
       <c r="F76" s="3">
         <v>69</v>
       </c>
@@ -3609,17 +3661,22 @@
         <v>1</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L76" s="7"/>
     </row>
-    <row r="77" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="26"/>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
       <c r="F77" s="3">
         <v>70</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I77" s="7"/>
       <c r="J77" s="3" t="s">
@@ -3630,7 +3687,12 @@
       </c>
       <c r="L77" s="7"/>
     </row>
-    <row r="78" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="26"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
       <c r="F78" s="3">
         <v>71</v>
       </c>
@@ -3647,38 +3709,40 @@
       </c>
       <c r="L78" s="7"/>
     </row>
-    <row r="79" spans="4:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:12" ht="12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="26"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
       <c r="F79" s="3">
         <v>72</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L79" s="7"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" selectLockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F8:L79">
-    <sortCondition ref="F8:F79"/>
-  </sortState>
-  <mergeCells count="5">
-    <mergeCell ref="H7:L7"/>
+  <mergeCells count="6">
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="G5:L5"/>
     <mergeCell ref="F2:L2"/>
     <mergeCell ref="G3:L3"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="A2:E79"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="whole" errorStyle="information" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Numeric entry" error="Please enter a whole number greater or equal to 0. Pres ESC to Cancel.a_x000a_nd re-try. _x000a_Thanks." sqref="I8:I79 L8:L79" xr:uid="{EB89CE4D-1741-47A3-811F-22E0FA8FD430}">
+    <dataValidation type="whole" errorStyle="information" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Numeric entry" error="Please enter a whole number greater or equal to 0. Pres ESC to Cancel.a_x000a_nd re-try. _x000a_Thanks." sqref="I8:I79 L8:L79" xr:uid="{ED9ADB03-6726-458D-A03C-536C4AC69775}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
